--- a/output_excel/16813660.xlsx
+++ b/output_excel/16813660.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -575,11 +575,11 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>P15 | CONEX. | 112,5KVA | INSTALAR | C09X600112,5KVASMFL112,5KVAL1(1) | P10 | BF-A | M10X600112,5KVAS45(3)112,5KVAL1(1) | TX16 | Q/R | BF-A | (DCIM) | REAPL. | 112,5KVA | 13M | FORA | 32.86 | (DCIM)</t>
+          <t>CONEX. | 1 | INSTALAR | C09X600112,5KVASMFL112,5KVAL1(1) | BF-A | M10X600112,5KVAS45(3)112,5KVAL1(1) | TX16 | Q/R</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>P10 | 32.86 | Q/R | (DCIM) | P15 | (DCIM) | C09X600112,5KVASMFL112,5KVAL1(1) | CONEX. | 46.17 | 112,5KVA | (DCIM) | BF-A | TX16 | INSTALAR | V9-10 | 1x3x70(70)AXNI(5AZN) | BF-A | 2x1/0AN(4ANA) | REAPL. | M10X600112,5KVAS45(3)112,5KVAL1(1) | P9 | 112,5KVA | CONEX. | 13M</t>
+          <t>Q/R | C09X600112,5KVASMFL112,5KVAL1(1) | 32.86 | (DCIM) | (DCIM) | 1 | BF-A | (DCIM) | TX16 | CONEX. | INSTALAR</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -669,11 +669,11 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | CONEX. | P9 | 32.86 | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | (DCIM) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 112,5KVA | ESTR. | INSTALAR | BF-A | TX10 | Q/R | (DCIM) | 46.17 | Q/R | C09X600112,5KVASMFL112,5KVAL1(1) | &gt; | TX16 | P10 | TX16 | BF-A | 112,5KVA | POSTE | 46.07M | BF-A | REAPL. | V8-9 | 46.07M | INSTALAR | 112,5KVA</t>
+          <t>CONEX. | (DCIM) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | ESTR. | 2 | BF-A | 32.86 | INSTALAR | (DCIM) | TX10</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | P9 | ESTR. | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 46.07M | (DCIM) | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | Q/R | 112,5KVA | BF-A | (DCIM) | 46.07M | 32.86 | TX10 | INSTALAR | &gt; | V8-9 | 46.17 | TX16 | 1x3x70(70)AXNI(5AZN) | POSTE | 2x1/0AN(4ANA) | (DCIM) | Q/R | 112,5KVA112,5KVA40M</t>
+          <t>CONEX. | ESTR. | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 46.07M | (DCIM) | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | Q/R | 2</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -763,7 +763,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1x3x70(70)AXNI(5AZN) | V8-9 | 2x1/0AN(4ANA) | 46.07M | 46.07M | P9 | (DCIM) | 46.17 | 32.86 | CONEX. | (DCIM) | 2x1/0AN(4ANA)</t>
+          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 46.07M | 46.07M</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -808,7 +808,7 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>V13-14 | 59.48M | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 59.48M | P33 | 30M</t>
+          <t>59.48M | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 59.48M</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | INSTALAR | 30K | 112,5KVA | BF-A | P14 | 1x2x4AC | BF-A | TX10 | QX16 | BF-A | TX16 | C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | 37.05M | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | &gt; | BF-A | BF-A | MEIO | ANCORAR | TX16 | 3x336AN | 2x1/0AN(4ANA) | REAPL. | AVENIDA | BT | 1x3x70(70)AX | CORDOALHA | REAPL. | CABOS | VÃO | CAMPO | BT | ANCORAR | DIVISA | ANCORAR | BT | IP | 112,5KVA | 112,5KVA | (KL) | 30M | C09x300,SMTG,IP | BF-A | 112,5KVA | (DCIM) | CABOS | BT | 175ET005296879112,5KVA10M | 30K112,5KVA | CABOS | 30K | P13 | 30K | 3x336AN | (DCIM) | CONEX. | V1-9 | 59.48M</t>
+          <t>CONEX. | INSTALAR | 3 | 1 | BF-A | 4 | BF-A | TX10 | QX16 | BF-A | TX16 | C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | 37.05M | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -906,11 +906,11 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | P8 | ANCORAR | M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | ESTR. | BCU | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | 112,5KVA | ESTR. | 112,5KVA | BF-A | Ê | TX10 | INSTALAR | CABOS | &gt; | 53.29M | V7-8 | TX16 | (DCIM) | 112,5KVA | 3. | 112,5KVA | 3x336AN | 112,5KVA | V1-9 | 112,5KVA | (DCIM) | 1x2x4AC | 1x3x70(70)AXNI(5AZN) | POSTE | 2X1/0AN( | 112,5KVA112,5KVA70M</t>
+          <t>CONEX. | 1RU6A | M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | ESTR. | 1RU6A | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | 112,5KVA | ESTR. | 1 | BF-A</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P33 | (DCIM) | 3x336AN | 59.48M | CABOS | (DCIM) | BT | 30K | 112,5KVA | V1-9 | 30M | CONEX. | (KL) | 2x1/0AN(4ANA) | 59.48M | 30K | DIVISA | 112,5KVA | INSTALAR | 30K | ANCORAR | 30K112,5KVA | &gt; | TX16 | CABOS | TX10 | CAMPO | BF-A | Nº307/SNº | 30K | BF-A | (DCIM) | 15KV_1F1(A)112,5KVA10M | C09x300,SMTG,IP | CABOS | P14 | 4x1/0AN | 30K | 112,5KVA | CABOS | 30K | (DCIM) | 30K | CONEX. | BT | V1-9 | FERRAGEM | BT | 30K | 112,5KVA | (KL) | (DCIM) | 1x3x70(70)AXNI(5AZN) | 112,5KVA | 112,5KVA | BF-A | AVENIDA | (DCIM) | IP | 112,5KVA | SUBST. | (DCIM) | CONEX. | V13-14 | 112,5KVA | (DCIM) | CAMPO | 112,5KVA | 30K | CABOS | 3x336AN | 30K | 1x2x4AC | 30K | 30K | CONEX. | 2x1/0AN(4AN) | 30K | 112,5KVA | (DCIM) | 112,5KVA | (KL) | (DCIM) | 112,5KVA | ANCORAR | (DCIM) | 112,5KVA | CONEX. | BT | (DCIM)</t>
+          <t>(DCIM) | 3x336AN | CABOS | BT | 112,5KVA | (DCIM) | 0 | (KL) | 9 | CONEX. | 112,5KVA | 3 | 1RU6A | 0 | 0112,5KVA | CAMPO | CABOS | 59.48M | (DCIM) | DIVISA | 2x1/0AN(4ANA) | CABOS | C09x300,SMTG,IP | Nº307/SNº | BT</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -992,27 +992,19 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>MADEIRA</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>P13 | 30M | VÃO | REAPL. | BF-A | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | REAPL. | C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | BF-A | TX16 | ESTR. | CORDOALHA | BF-A | BF-A | TX16 | 175ET005296879112,5KVA10M | 1x2x4AC | QX16 | &gt; | BF-A | 112,5KVA | TX10 | BF-A | BF-A | DIVISA | 2x1/0AN(4ANA) | SUBST. | 30K | MEIO | ANCORAR | Nº311/SNº | ANCORAR | BT | INSTALAR | 3x336AN | AVENIDA | IP | BT | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>30M | INSTALAR | 2x1/0AN(4ANA) | (DCIM) | 3x336AN | (DCIM) | TX10 | BF-A | 3 | DIVISA | &gt; | CABOS | 0 | TX16 | 59.48M | 9 | BT | 59.48M | CONEX. | 112,5KVA</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1049,7 +1041,7 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>V7-8 | 1x3x70(70)AXNI(5AZN) | 1x2x4AC | 2X1/0AN( | 112,5KVA | 3x336AN | 112,5KVA | (DCIM) | 112,5KVA | 3. | ANCORAR | AVENIDA | 112,5KVA | 112,5KVA | V1-9 | (KL) | (DCIM) | (DCIM) | Z | 112,5KVA | 53.29M | ANCORAR | BCU | P8 | GUSMAO | CONEX. | PODA | ANCORAR | BCU | 112,5KVA | ESTR. | Ê | CABOS | ESTR.</t>
+          <t>1x3x70(70)AXNI(5AZN) | 4 | 2X1/0AN( | 112,5KVA | 3x336AN | 112,5KVA | (DCIM) | 5 | 3. | 1RU6A | AVENIDA | 112,5KVA | 2 | (KL) | 9 | (DCIM) | Z | (DCIM) | 112,5KVA | 53.29M | 1RU6A</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -1077,36 +1069,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+          <t>V12-13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47m</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | P13 | UBIRATÃ | 30M | RUA | INSTALAR | 30K | (DCIM) | BF-A | 30K | (DCIM) | TX10 | POSTE | CLANDESTINOS: | V1-9 | 112,5KVA | MEIO | CONEX. | 30K | .47M | BT | 30K | CONEX. | 30K | 30K | CORDOALHA | ANCORAR | 30K | 4x1/0AN | 3x336AN | INSTALAR | P33 | 30K | 30K | ESTR. | &gt; | (DCIM) | 112,5KVA | VÃO | 30K | CABOS | 59.48M | 3x336AN | 112,5KVA | TX16 | 1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | CABOS | C09X300112,5KVASMTG112,5KVAIP | (DCIM) | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>1x3x120(70)AX | 0 | 0 | 7 | 1x3x120(70)AX | CONEX. | 3 | CONEX. | 3x336AN | 6 | 112,5KVA | CONEX. | 3 | 0 | 4x1/0AN | 3x336AN | .4 | 1 | 1 | CONEX. | 7 | 1x3x70(70)AXNI(5AZN) | 4 | (DCIM) | 3x336AN | (DCIM) | 6 | 3 | .47M | 1</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1126,32 +1114,36 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>V12-13</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32m</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | 30K | 30K | 37,5KVA | 1x3x120(70)AX | CONEX. | 30K | CONEX. | 3x336AN | 3x336AN | CONEX. | 112,5KVA | 30K | 30K | 3x336AN | 4x1/0AN | V12-13 | .4 | 112,5KVA | 112,5KVA | 1x3x70(70)AXNI(5AZN) | CONEX. | 37,5KVA | 1x2x4AC | (DCIM) | 3x336AN | (DCIM) | 3x336AN | P31 | 30K | .47M | 112,5KVA | 32M | RUA | INSTALAR | INSTALAR</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+          <t>1 | INSTALAR | .47M | 3 | 6 | (DCIM) | RUA | 3x336AN | C09X300112,5KVASMTG112,5KVAIP | (DCIM) | 32M | 7 | 1x3x70(70)AXNI(5AZN) | 3x336AN | .4 | 3 | CONEX. | POSTE | UBIRATÃ | 6 | CAPAO | 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1176,31 +1168,23 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>112,5KVA | P31 | 3x336AN | 30K | (DCIM) | .47M | 3x336AN | (DCIM) | 37,5KVA | 1x3x70(70)AXNI(5AZN) | INSTALAR | RUA | 3x336AN | .4 | 32M | CONEX. | 30K | C09X300112,5KVASMTG112,5KVAIP | 3x336AN | 1x3x120(70)AX | 30K | 3x336AN | UBIRATÃ | 1x3x120(70)AX | 112,5KVA | POSTE | 30K | 30K | 4x1/0AN | 37,5KVA | CAPAO | INSTALAR | CONEX. | 112,5KVA | POSTE | TX16 | LADO | &gt; | 30K | CONEX. | BF-A | 112,5KVA112,5KVA70M | TX10 | CONEX. | 1x2x4AC | BF-A | 112,5KVA | 112,5KVA | V12-13 | BF-A | SUBST. | P13 | C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | CLANDESTINOS: | CONEX. | M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>CONEX. | Q/R | (DCIM) | 1 | 0 | (DCIM) | CONEX. | 0 | 3 | 9 | 0 | CONEX. | ESTR. | 0 | 3 | 1 | 112,5KVA | BF-A | 0 | CABOS | BT | 0 | 1 | CONEX. | 4 | 112,5KVA | BF-A | CABOS | 1 | BT | 3 | 6 | CONEX. | (DCIM) | (DCIM) | 1 | BF-A | 3 | INSTALAR | 0 | CAMPO | 1RU6A | (DCIM) | &gt; | (DCIM)112,5KVA | 112,5KVA(KL) | AVENIDA | (KL) | BT | 112,5KVA | 1 | 1 | CONEX. | 51.47M | CAMPO | (DCIM) | PODA | (DCIM) | 1 | 1 | (KL) | 1 | POSTE | 6 | (DCIM) | AV. | (DCIM) | 112,5KVA | 1 | 112,5KVA | 51.47M | (DCIM) | (DCIM) | CAMPO | 1 | GUSMAO | CAMPO | 112,5KVA | 1x3x70(70)AXNI(5AZN) | 7</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1225,23 +1209,31 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | P7x | (DCIM) | Q/R | 112,5KVA | (DCIM) | 30K | CONEX. | 30K | 30K | V1-9 | 112,5KVA | CONEX. | 30K | 30K | ESTR. | BF-A | 30K | 112,5KVA | BT | 30K | 112,5KVA | CABOS | CONEX. | 30K | BF-A | BT | 112,5KVA | 112,5KVA | 1x2x4AC | PODA | CABOS | CONEX. | 3x336AN | INSTALAR | 30K | 112,5KVA | (DCIM) | BF-A | (DCIM) | 30K | 30K | ANCORAR | CAMPO | GUSMAO | V6-7 | &gt; | (DCIM) | AVENIDA | (DCIM)112,5KVA | 51.47M | 112,5KVA(KL) | BCU | BT | (KL) | 112,5KVA | CONEX. | 112,5KVA | 1x3x70(70)AXNI(5AZN) | 112,5KVA | 51.47M | CAMPO | ANCORAR | 112,5KVA | (DCIM) | (DCIM) | POSTE | (DCIM) | 53.29M | (KL) | 3x336AN | 112,5KVA | 112,5KVA | 112,5KVA | V1-9</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+          <t>32M | 1 | (DCIM) | 7 | POSTE | .4 | INSTALAR | 3 | INSTALAR | 3x336AN | (DCIM) | 6 | 6 | 1x3x70(70)AXNI(5AZN) | C09X300112,5KVASMTG112,5KVAIP | 3 | 3x336AN | .47M | &gt; | TX10 | CONEX. | BF-A | TX16 | 3x336AN | 1 | 1x3x120(70)AX | 112,5KVA | CAPAO | 0 | 0 | BF-A | RUA | 4x1/0AN | 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1261,24 +1253,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>V11-12</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50.53m</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>P12 | 32M | 30K | 2x1/0AN(4AN) | 1x2x4AC | (DCIM) | CABOS | 112,5KVA | ANCORAR | 112,5KVA | (KL) | 30K | 112,5KVA | 30K | (DCIM) | VÃO | 112,5KVA | 30K | BT | (DCIM) | CONEX. | 112,5KVA | (DCIM) | 30K | CAMPO | BT | FERRAGEM | (DCIM) | 112,5KVA | 112,5KVA | CABOS | (KL) | 112,5KVA | 112,5KVA | 30K | (DCIM) | 30K | 112,5KVA | (DCIM) | CORDOALHA | 30K | (DCIM) | CONEX. | 112,5KVA | (DCIM) | V1-9 | CAMPO | 30K | (DCIM) | TX16 | &gt; | BF-A | 15KV_1F1(A)112,5KVA10M | TX10 | BF-A | MEIO | 30K | BF-A | 2x1/0AN(4ANA) | DIVISA | SUBST. | ESTR. | Nº307/SNº | CLANDESTINOS: | INSTALAR</t>
+          <t>50.53M | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 50.53M</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1307,19 +1303,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>V11-12</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50.53m</t>
+          <t>51.47m</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50.53M | V11-12 | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 50.53M | P12 | 25M | P32 | LADO</t>
+          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 51.47M | 51.47M</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1352,23 +1348,23 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>MADEIRA</t>
+          <t>CONCRETO</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>9m</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP | C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | 112,5KVA | CONEX. | ESTR. | BF-A | INSTALAR | TX10 | P12 | &gt; | POSTE | CLANDESTINOS: | TX16 | MEIO | 32M | POSTE | P32 | 50.53M | INSTALAR | CORDOALHA | ESTR. | BF-A | VÃO | C09X300112,5KVASMPI112,5KVAIP | 112,5KVA112,5KVA70M | CAPAO | 25M | P31</t>
+          <t>25M | SMPI | INSTALAR | C09X300112,5KVASMPI112,5KVAIP | C12X600112,5KVACE3112,5KVAS144-1112,5KVAIP | 50.53M | 50.53M</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1396,28 +1392,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>V6-7</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>51.47m</t>
-        </is>
-      </c>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>V6-7 | 1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 51.47M | 51.47M | P7x | CONEX. | V5-6</t>
+          <t>25M | VÃO | CORDOALHA | VIA | CABOS | IP | MEIO | ESTR. | COMPARTILHANTES</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1446,31 +1438,23 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25M | P32 | SMPI | INSTALAR | C09X300112,5KVASMPI112,5KVAIP | C12X600112,5KVACE3112,5KVAS144-1112,5KVAIP | 50.53M | 50.53M | 4x1/0AN | P11 | POSTE | 1x3x70(70)AXNI(5AZN) | LADO | &gt; | TX16 | TX10 | BF-A | BF-A | V11-12 | P12 | 112,5KVA | P13112,5KVA70M | CAPAO | CONEX.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>CONEX. | 31.61M | 31.61M | Q/R</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1490,36 +1474,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>MADEIRA</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
+          <t>V5-6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>31.61m</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>P11 | CABOS | VIA | 25M | IP | COMPARTILHANTES | VÃO | COMPARTILHANTES | CONDIÇÕES | CORDOALHA | P31 | ORÇAMENTO | P16 | BF-A | SUBST. | MEIO | 175ET005296879 | 112,5KVA112,5KVA70M | CLANDESTINOS: | ORÇAMENTO | BF-A | ESTR. | LADO | TX16 | CAPAO | CLANDESTINOS: | REFERÊNCIA | ESTR. | &gt; | BANDEIRA | PARA | POSTE | M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP | C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | TERMINAL | TX10 | 175ET005296879</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>31.61M | 2x1/0AN(4ANA) | 1x3x70(70)AXNI(5AZN) | 1x3x70(70)AXNI(5AZN) | 31.61M | 2x1/0AN(4ANA) | 12.55M | 12.55M</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1544,31 +1524,23 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | P6 | 31.61M | (DCIM) | CABOS | 3x336AN | S44(3) | (DCIM) | CABOS | C09X600112,5KVAL1(2)112,5KVAIP | Q/R | ESTR. | CAMPO | BT | (DCIM) | 112,5KVA | 31.61M | INSTALAR | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 12.55M | P5 | POSTE | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | (DCIM) | FERRAGEM | INSTALAR | 12.55M | POSTE | V5-6</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>CORDOALHA | RAMAIS | TRECHO | PODA | DOS | AVENIDA | TRÁFEGO | CLANDESTINOS: | CAMINHÃO | REFERÊNCIA | PARA | LOCAL</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1588,28 +1560,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>V5-6</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>31.61m</t>
-        </is>
-      </c>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31.61M | V4-5 | 2x1/0AN(4ANA) | 1x3x70(70)AXNI(5AZN) | 1x3x70(70)AXNI(5AZN) | V5-6 | 31.61M | 2x1/0AN(4ANA) | 12.55M | 12.55M | P6 | CONEX. | (DCIM) | 51.47M | P5 | 51.47M</t>
+          <t>PODA | RAMAIS | AVENIDA | DOS | CORDOALHA | TRECHO | REFERÊNCIA</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1633,36 +1601,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+          <t>V4-5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>31.61m</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25M | SMPI | C12X600112,5KVACE3112,5KVAS144-1112,5KVAIP | P32 | C09X300112,5KVASMPI112,5KVAIP | INSTALAR | P11 | &gt; | TX16 | TX10 | BF-A | 112,5KVA | BF-A | P13112,5KVA70M | 50.53M | SMFL | LADO | POSTE | BF-A | 50.53M | 4x1/0AN | SUBST. | S45(3) | CAPAO | 1x3x70(70)AXNI(5AZN) | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 2x1/0AN(4ANA) | 31.61M | 12.55M | 1x3x70(70)AXNI(5AZN) | 12.55M</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1687,23 +1651,31 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>CORDOALHA | RAMAIS | TRECHO | PODA | DOS | AVENIDA | TRÁFEGO | CLANDESTINOS: | CAMINHÃO | REFERÊNCIA | PARA | LOCAL | CLANDESTINOS: | CLANDESTINOS: | 175ET005296879 | 30K | ORÇAMENTO | ORÇAMENTO | CONDIÇÕES | TP</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+          <t>FERRAGEM | (DCIM) | CMB | GD | 12.55M | 175ET005296879 | C09X600112,5KVAL1(2)112,5KVAIP | 12.55M | SMPI | 529687 | S44(3) | SMFL112,5KVAS45(3) | C12X600112,5KVACE4112,5KVAIP | CABOS | (DCIM) | 31.61M | CAMPO | (DCIM)</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1728,23 +1700,31 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P4-30</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>RAMAIS | PODA | AVENIDA | DOS | CORDOALHA | TRECHO | REFERÊNCIA | TRÁFEGO | 175ET005296879 | PARA | CLANDESTINOS: | CLANDESTINOS: | CAMINHÃO | CLANDESTINOS: | LOCAL | 30K | ORÇAMENTO | ORÇAMENTO | TP | CONDIÇÕES | P16 | P31 | (KL)</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+          <t>C12X600112,5KVACE4112,5KVAIP | SMFL112,5KVAS45(3) | MT | SMPI | 3x70AX(5AZN) | 1x3x70(70)AXNI(5AZN) | 2x1/0AN(4AN)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1764,28 +1744,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>V4-5</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>31.61m</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | 1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 2x1/0AN(4ANA) | 31.61M | 1x3x70(70)AXNI(5AZN) | 12.55M | V5-6 | 31.61M | 12.55M | P6 | CONEX.</t>
+          <t>S43(3) | 35.64M | SMTG | 3x70AX(5AZN)</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1809,36 +1785,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+          <t>V2-3</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>31.18m</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM | (DCIM) | P5 | CMB | P4-30 | GD | P31 | C09X600112,5KVAL1(2)112,5KVAIP | 12.55M | 175ET005296879 | S44(3) | 175ET005296879 | 12.55M | CABOS | (DCIM) | CAMPO | (DCIM) | 31.61M | SMPI | (DCIM) | 3x336AN | CABOS | BT | 112,5KVA | INSTALAR | SMFL112,5KVAS45(3) | POSTE</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>31.18M | 31.18M | 31.18M | 3x70AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1863,7 +1835,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>P4-30</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1879,11 +1851,11 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>175ET005296879 | 175ET005296879 | CMB | P4-30 | GD | P31 | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | FERRAGEM | 15KV_PDRT(ABC) | S45(3) | 175ET005296879 | P5 | P2 | (DCIM) | SMFL | 112,5KVA | 175ET005296879112,5KVAD_TF | P11 | BF-A | TX10 | C09X600112,5KVAL1(2)112,5KVAIP | 112,5KVA | 31.18M</t>
+          <t>S43(3) | SMTG | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP | 1 | BF-A | TX16</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1907,24 +1879,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>V1-2</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>35.64m</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P31 | GD | P4-30 | 175ET005296879 | CMB | 175ET005296879 | 31.18M | P2 | FERRAGEM | 31.18M | (DCIM) | P5 | V2-3 | 3x70AX(5AZN) | 31.18M | MT | 15KV_PDRT(ABC) | SMPI | 1x3x70(70)AXNI(5AZN) | SMFL112,5KVAS45(3) | 175ET005296879</t>
+          <t>35.64M | 2x1/0AN(4AN) | 1x3x70(70)AXNI(5AZN) | 3x70AX(5AZN) | 35.64M | MT | 35.64M</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -1932,194 +1908,6 @@
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>16813660</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>POSTE</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>S43(3) | 35.64M | P1-11 | SMTG | V1-2 | 3x70AX(5AZN) | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP | 35.64M | MT | P2 | 35.64M | 112,5KVA | BF-A | TX16 | 1x3x70(70)AXNI(5AZN) | BF-A | CONEX. | 2x1/0AN(4AN) | 31.18M</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>16813660</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>VAO</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>V2-3</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>31.18m</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>2x1/0AN(4AN) | 1x3x70(70)AXNI(5AZN) | MT | 3x70AX(5AZN) | V2-3 | 31.18M | 31.18M | C12X600112,5KVACE4112,5KVAIP | 31.18M | SMFL112,5KVAS45(3) | SMPI</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>16813660</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>POSTE</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>P1-11 | 35.64M | 35.64M | S45(3) | SMFL | C12X300112,5KVACE2112,5KVAL1(2)112,5KVAIP | ESTRADA | 112,5KVA | BF-A | TX16 | 35.64M | S43(3) | BF-A | SMTG | CAPAO | CONEX. | CONEX. | 3x70AX(5AZN) | BF-A | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP | TX16 | V1-2</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>16813660</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>VAO</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>V1-2</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>35.64m</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>35.64M | 2x1/0AN(4AN) | 1x3x70(70)AXNI(5AZN) | 3x70AX(5AZN) | 35.64M | MT | 35.64M | V1-2 | ESTRADA | P1-11</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>

--- a/output_excel/16813660.xlsx
+++ b/output_excel/16813660.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -563,30 +581,33 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | 1 | INSTALAR | C09X600112,5KVASMFL112,5KVAL1(1) | BF-A | M10X600112,5KVAS45(3)112,5KVAL1(1) | TX16 | Q/R</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>C09X600112,5KVASMFL112,5KVAL1(1) | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | M10X600112,5KVAS45(3)112,5KVAL1(1) | CONEX. | P10 | Q/R (DCIM) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | V9-10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -612,30 +633,33 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Q/R | C09X600112,5KVASMFL112,5KVAL1(1) | 32.86 | (DCIM) | (DCIM) | 1 | BF-A | (DCIM) | TX16 | CONEX. | INSTALAR</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>C09X600112,5KVASMFL112,5KVAL1(1) | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | M10X600112,5KVAS45(3)112,5KVAL1(1) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | P10 | Q/R (DCIM) | CONEX. | 2x1/0AN(4ANA) 46.17</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -660,27 +684,30 @@
           <t>V9-10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46.07m</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>CONEX. | (DCIM) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | ESTR. | 2 | BF-A | 32.86 | INSTALAR | (DCIM) | TX10</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+          <t>46.07m</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 32.86 (DCIM) | 46.07M | 2x1/0AN(4ANA) 1x3x70(70)AXNI(5AZN) 46.07M | (DCIM) | P15 1 INSTALAR 2 V1-3 TX16 2 V1-3 REAPL. 112,5KVA 13M | 12112,5KVA40M 2 V1-3 SUBST. | M10X600112,5KVAS45(3)112,5KVAL1(1)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -706,30 +733,33 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>MADEIRA</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | ESTR. | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | 46.07M | (DCIM) | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | Q/R | 2</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | C09X600112,5KVASMFL112,5KVAL1(1) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | P9 | CONEX. ESTR. Q/R | 2 2 V1-3 TX10 &gt; TX16 | INSTALAR POSTE</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -754,27 +784,30 @@
           <t>V8-9</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46.07m</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 46.07M | 46.07M</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
+          <t>46.07m</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2x1/0AN(4ANA) 1x3x70(70)AXNI(5AZN) 46.07M | 46.07M | 32.86 (DCIM) | (DCIM) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | V8-9 | CONEX. M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | P15 1 INSTALAR 2 V1-3 TX16 2 V1-3 REAPL. 112,5KVA 13M</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -799,27 +832,30 @@
           <t>V13-14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59.48m</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59.48M | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 59.48M</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
+          <t>59.48m</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4x1/0AN 1x3x70(70)AXNI(5AZN) 59.48M | 59.48M | 30M | 2 V1-3 15112,5KVA10M 2 V1-3 SUBST. | (DCIM) 1 0 CONEX. 3 0 0112,5KVA2 CS's 4 3 2x1/0AN(4AN) (DCIM)112,5KVA | V13-14 | 3 .47M UBIRATÃ | 37.05M</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -845,30 +881,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | INSTALAR | 3 | 1 | BF-A | 4 | BF-A | TX10 | QX16 | BF-A | TX16 | C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | 37.05M | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MADEIRA</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) C09x300,SMTG,IP112,5KVA | P14 CONEX. | 3 1 2 V1-3 2 V1-3 TX10 QX16 &gt; 2 V1-3 REAPL. TX16 | 4 2 V1-3 TX16 2 V1-3 REAPL. | INSTALAR 1x4ANA DIVISA | BT 1x3x70(70)AX | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) BT CARGA112,5KVA</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -894,30 +933,33 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>MADEIRA</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | 1RU6A | M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | ESTR. | 1RU6A | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | 112,5KVA | ESTR. | 1 | BF-A</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | CONEX. M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | xP8 | ESTR. | 1RU6A 1RU6A 112,5KVA | ESTR. Ê 2 CS's | 1 2 V1-3 TX10 &gt; TX16</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -943,30 +985,33 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | 3x336AN | CABOS | BT | 112,5KVA | (DCIM) | 0 | (KL) | 9 | CONEX. | 112,5KVA | 3 | 1RU6A | 0 | 0112,5KVA | CAMPO | CABOS | 59.48M | (DCIM) | DIVISA | 2x1/0AN(4ANA) | CABOS | C09x300,SMTG,IP | Nº307/SNº | BT</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>(DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) C09x300,SMTG,IP112,5KVA | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) BT CARGA112,5KVA | (DCIM) 1 0 CONEX. 3 0 0112,5KVA2 CS's 4 3 2x1/0AN(4AN) (DCIM)112,5KVA | (DCIM) 1x4ANA 2 CS's BT 112,5KVA (KL) 112,5KVA 1RU6A CAMPO 2 CS's BT | P33 | INSTALAR 1x4ANA DIVISA | Nº307/SNº</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -994,20 +1039,31 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30M | INSTALAR | 2x1/0AN(4ANA) | (DCIM) | 3x336AN | (DCIM) | TX10 | BF-A | 3 | DIVISA | &gt; | CABOS | 0 | TX16 | 59.48M | 9 | BT | 59.48M | CONEX. | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>(DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) BT CARGA112,5KVA | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) C09x300,SMTG,IP112,5KVA | M10X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP C09X300112,5KVASMPI112,5KVAL1(2)112,5KVAIP | (DCIM) 1 0 CONEX. 3 0 0112,5KVA2 CS's 4 3 2x1/0AN(4AN) (DCIM)112,5KVA | P33 | INSTALAR 1x4ANA DIVISA | 3 2 V1-3 TX10 &gt; TX16 | (DCIM) 1x4ANA 2 CS's BT 112,5KVA (KL) 112,5KVA 1RU6A CAMPO 2 CS's BT</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1032,27 +1088,30 @@
           <t>V7-8</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>53.29m</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1x3x70(70)AXNI(5AZN) | 4 | 2X1/0AN( | 112,5KVA | 3x336AN | 112,5KVA | (DCIM) | 5 | 3. | 1RU6A | AVENIDA | 112,5KVA | 2 | (KL) | 9 | (DCIM) | Z | (DCIM) | 112,5KVA | 53.29M | 1RU6A</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
+          <t>53.29m</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>-23.15982288 2 9 (DCIM) | 53.29M | CONEX. M10X300112,5KVAS43(1)112,5KVAS44(2)112,5KVAL1(1)112,5KVAIP | 46.07M | V7-8 | 1x3x70(70)AXNI(5AZN) | 2X1/0AN( 4 112,5KVA 1x4ANA 112,5KVA (DCIM) 5</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1077,27 +1136,30 @@
           <t>V12-13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47m</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | 0 | 0 | 7 | 1x3x120(70)AX | CONEX. | 3 | CONEX. | 3x336AN | 6 | 112,5KVA | CONEX. | 3 | 0 | 4x1/0AN | 3x336AN | .4 | 1 | 1 | CONEX. | 7 | 1x3x70(70)AXNI(5AZN) | 4 | (DCIM) | 3x336AN | (DCIM) | 6 | 3 | .47M | 1</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
+          <t>32m</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4 CONEX. 1 4x1/0AN 0 112,5KVA 1x4ANA 6 3 .4 7 (DCIM) | 32M | 3 .47M UBIRATÃ | 2 V1-3 2112,5KVA70M CAPAO LADO 2 V1-3 SUBST. | 50.53M | 1 CONEX. 3 CONEX. 7 0 1x3x120(70)AX 0 1x3x120(70)AX CONEX. 1x4ANA 1x3x70(70)AXNI(5AZN) | V12-13 | 1x4ANA (DCIM) 6</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1123,30 +1185,33 @@
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1 | INSTALAR | .47M | 3 | 6 | (DCIM) | RUA | 3x336AN | C09X300112,5KVASMTG112,5KVAIP | (DCIM) | 32M | 7 | 1x3x70(70)AXNI(5AZN) | 3x336AN | .4 | 3 | CONEX. | POSTE | UBIRATÃ | 6 | CAPAO | 1x3x120(70)AX</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MADEIRA</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | C09X300112,5KVASMTG112,5KVAIP | 1x4ANA (DCIM) 6 | INSTALAR POSTE | 1 INSTALAR 2 V1-3 TX10 &gt; TX16 POSTE | 1 CONEX. 3 CONEX. 7 0 1x3x120(70)AX 0 1x3x120(70)AX CONEX. 1x4ANA 1x3x70(70)AXNI(5AZN) | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) BT CARGA112,5KVA</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1174,20 +1239,31 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | Q/R | (DCIM) | 1 | 0 | (DCIM) | CONEX. | 0 | 3 | 9 | 0 | CONEX. | ESTR. | 0 | 3 | 1 | 112,5KVA | BF-A | 0 | CABOS | BT | 0 | 1 | CONEX. | 4 | 112,5KVA | BF-A | CABOS | 1 | BT | 3 | 6 | CONEX. | (DCIM) | (DCIM) | 1 | BF-A | 3 | INSTALAR | 0 | CAMPO | 1RU6A | (DCIM) | &gt; | (DCIM)112,5KVA | 112,5KVA(KL) | AVENIDA | (KL) | BT | 112,5KVA | 1 | 1 | CONEX. | 51.47M | CAMPO | (DCIM) | PODA | (DCIM) | 1 | 1 | (KL) | 1 | POSTE | 6 | (DCIM) | AV. | (DCIM) | 112,5KVA | 1 | 112,5KVA | 51.47M | (DCIM) | (DCIM) | CAMPO | 1 | GUSMAO | CAMPO | 112,5KVA | 1x3x70(70)AXNI(5AZN) | 7</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP INSTALAR POSTE | (DCIM) 0 9 CONEX. 3 0 0112,5KVA2 CS's (DCIM) CAMPO (DCIM)112,5KVA(KL) | (DCIM) 1 0 CONEX. 3 0 0112,5KVA2 CS's 4 3 (DCIM) 3 (DCIM)112,5KVA(KL) | P7x CONEX. Q/R | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | ESTR.</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1213,30 +1289,33 @@
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32M | 1 | (DCIM) | 7 | POSTE | .4 | INSTALAR | 3 | INSTALAR | 3x336AN | (DCIM) | 6 | 6 | 1x3x70(70)AXNI(5AZN) | C09X300112,5KVASMTG112,5KVAIP | 3 | 3x336AN | .47M | &gt; | TX10 | CONEX. | BF-A | TX16 | 3x336AN | 1 | 1x3x120(70)AX | 112,5KVA | CAPAO | 0 | 0 | BF-A | RUA | 4x1/0AN | 1x3x120(70)AX</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MADEIRA</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | C09X300112,5KVASMTG112,5KVAIP | 1 INSTALAR 2 V1-3 TX10 &gt; TX16 POSTE | 1x4ANA (DCIM) 6 | 1 CONEX. 3 CONEX. 7 0 1x3x120(70)AX 0 1x3x120(70)AX CONEX. 1x4ANA 1x3x70(70)AXNI(5AZN) | INSTALAR POSTE | C09X300112,5KVASMPI112,5KVAIP</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1261,27 +1340,30 @@
           <t>V11-12</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50.53m</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50.53M | 1x3x70(70)AXNI(5AZN) | 4x1/0AN | 50.53M</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n">
+          <t>50.53m</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4x1/0AN 50.53M | 50.53M | 25M | 4 CONEX. 1 4x1/0AN 0 112,5KVA 1x4ANA 6 3 .4 7 (DCIM) | 32M | V11-12 | 1x3x70(70)AXNI(5AZN) | 2 V1-3 13112,5KVA70M 2 V1-3 SUBST.</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1306,27 +1388,30 @@
           <t>V6-7</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51.47m</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 51.47M | 51.47M</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n">
+          <t>51.47m</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2x1/0AN(4ANA) 51.47M | 51.47M | (DCIM) 1 0 CONEX. 3 0 0112,5KVA2 CS's 4 3 (DCIM) 3 (DCIM)112,5KVA(KL) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | -23.15982288 2 9 (DCIM) | 53.29M | 31.61M 31.61M | 1x3x70(70)AXNI(5AZN) V6-7</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1352,30 +1437,33 @@
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25M | SMPI | INSTALAR | C09X300112,5KVASMPI112,5KVAIP | C12X600112,5KVACE3112,5KVAS144-1112,5KVAIP | 50.53M | 50.53M</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE3112,5KVAS144-1112,5KVAIP SMPI | C09X300112,5KVASMPI112,5KVAIP | M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP 1 2 V1-3 TX16 2 V1-3 CONEX. | P32 | S45(3) SMFL | INSTALAR POSTE</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1403,20 +1491,31 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25M | VÃO | CORDOALHA | VIA | CABOS | IP | MEIO | ESTR. | COMPARTILHANTES</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MADEIRA</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>M10X600112,5KVAS44(4)112,5KVAL1(2)112,5KVAIP C09X600112,5KVASMPI112,5KVAL1(2)112,5KVAIP | C09X300112,5KVASMTG112,5KVAIP | C09X300112,5KVASMPI112,5KVAIP | ESTR. | VIA COMPARTILHANTES CONDIÇÕES | ESTR. | IP 175,175ET005296879 | P31 ORÇAMENTO</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1444,20 +1543,31 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | 31.61M | 31.61M | Q/R</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP INSTALAR POSTE | C09X600112,5KVAL1(2)112,5KVAIP | S44(3) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | P6 CONEX. | Q/R ESTR. | (DCIM) 2 CS's 1x4ANA (DCIM) 2 CS's CAMPO BT (DCIM) 112,5KVA INSTALAR POSTE | C12X600112,5KVACE4112,5KVAIP</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1482,27 +1592,30 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31.61m</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31.61M | 2x1/0AN(4ANA) | 1x3x70(70)AXNI(5AZN) | 1x3x70(70)AXNI(5AZN) | 31.61M | 2x1/0AN(4ANA) | 12.55M | 12.55M</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="n">
+          <t>51.47m</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>31.61M 31.61M | 2x1/0AN(4ANA) 12.55M | 12.55M (DCIM) 27.63m P5 | 51.47M | 2x1/0AN(4ANA) 51.47M | SMPI SMFL112,5KVAS45(3) | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | V4-5 1x3x70(70)AXNI(5AZN)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1530,20 +1643,23 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>CORDOALHA | RAMAIS | TRECHO | PODA | DOS | AVENIDA | TRÁFEGO | CLANDESTINOS: | CAMINHÃO | REFERÊNCIA | PARA | LOCAL</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="n">
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>AFASTADOR TRECHO | PODA | DOS RAMAIS | CLANDESTINOS: CAMINHÃO | PARA TRÁFEGO | CLANDESTINOS: REFERÊNCIA | CLANDESTINOS: LOCAL | P16 ORÇAMENTO AVENIDA</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1571,20 +1687,23 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>PODA | RAMAIS | AVENIDA | DOS | CORDOALHA | TRECHO | REFERÊNCIA</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n">
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>PODA | DOS RAMAIS | AFASTADOR TRECHO | CLANDESTINOS: REFERÊNCIA | PARA TRÁFEGO | P16 ORÇAMENTO AVENIDA | CLANDESTINOS: CAMINHÃO | CLANDESTINOS: LOCAL</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1609,27 +1728,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>31.61m</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1x3x70(70)AXNI(5AZN) | 2x1/0AN(4ANA) | 2x1/0AN(4ANA) | 31.61M | 12.55M | 1x3x70(70)AXNI(5AZN) | 12.55M</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="n">
+          <t>51.47m</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2x1/0AN(4ANA) 12.55M | 31.61M 31.61M | 12.55M (DCIM) 27.63m P5 | SMPI SMFL112,5KVAS45(3) | 51.47M | 2x1/0AN(4ANA) 51.47M | M10X300112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | V4-5 1x3x70(70)AXNI(5AZN)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1655,30 +1777,33 @@
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM | (DCIM) | CMB | GD | 12.55M | 175ET005296879 | C09X600112,5KVAL1(2)112,5KVAIP | 12.55M | SMPI | 529687 | S44(3) | SMFL112,5KVAS45(3) | C12X600112,5KVACE4112,5KVAIP | CABOS | (DCIM) | 31.61M | CAMPO | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | C09X600112,5KVAL1(2)112,5KVAIP | C12X600112,5KVACE4112,5KVAIP | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP 1 2 V1-3 TX16 2 V1-3 CONEX. | SMPI SMFL112,5KVAS45(3) | S44(3) | CARGA | C09X300112,5KVASMTG112,5KVAL1(1)112,5KVAIP INSTALAR POSTE</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1704,30 +1829,33 @@
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>C12X600112,5KVACE4112,5KVAIP | SMFL112,5KVAS45(3) | MT | SMPI | 3x70AX(5AZN) | 1x3x70(70)AXNI(5AZN) | 2x1/0AN(4AN)</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE4112,5KVAIP | SMPI SMFL112,5KVAS45(3) | MT V2-3 3x70AX(5AZN) | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | 1x3x70(70)AXNI(5AZN) | C09X600112,5KVAL1(2)112,5KVAIP | P31 GD | CARGA</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1755,20 +1883,31 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>S43(3) | 35.64M | SMTG | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP 1 2 V1-3 TX16 2 V1-3 CONEX. | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | S43(3) | C12X300112,5KVACE2112,5KVAL1(2)112,5KVAIP 2 2 V1-3 TX16 2 V1-3 CONEX. | S45(3) SMFL | P1-11 | P2 SMTG | V1-2</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1793,27 +1932,30 @@
           <t>V2-3</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>31.18m</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31.18M | 31.18M | 31.18M | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="n">
+          <t>31.18m</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>31.18M | 31.18M | 2x1/0AN(4AN) 31.18M | MT V2-3 3x70AX(5AZN) | P2 SMTG | MT 3x70AX(5AZN) | SMPI SMFL112,5KVAS45(3) | 2x1/0AN(4AN) 35.64M</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1839,30 +1981,33 @@
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>S43(3) | SMTG | C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP | 1 | BF-A | TX16</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>C12X1000112,5KVACE2-3LF112,5KVAS44(1)112,5KVAL1(2)112,5KVAIP 1 2 V1-3 TX16 2 V1-3 CONEX. | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAS150-0112,5KVAL1(2)112,5KVAIP | S43(3) | C12X300112,5KVACE2112,5KVAL1(2)112,5KVAIP 2 2 V1-3 TX16 2 V1-3 CONEX. | P2 SMTG | S45(3) SMFL | P1-11 | S45(3) SMFL</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1887,27 +2032,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>35.64m</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35.64M | 2x1/0AN(4AN) | 1x3x70(70)AXNI(5AZN) | 3x70AX(5AZN) | 35.64M | MT | 35.64M</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="n">
+          <t>35.64m</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2x1/0AN(4AN) 35.64M | MT 3x70AX(5AZN) | 35.64M | 35.64M | 31.18M | P2 SMTG | S45(3) SMFL | 31.18M</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
